--- a/data/trans_orig/IP26B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP26B-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25918</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>14532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28907</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>30933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>34555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51258</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33394</t>
+          <t>32945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48582</t>
+          <t>50071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73077</t>
+          <t>73381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96682</t>
+          <t>95394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42172</t>
+          <t>42425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37632</t>
+          <t>38065</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55081</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68621</t>
+          <t>68523</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91723</t>
+          <t>91997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18165</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>13908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27953</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25137</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48699</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77703</t>
+          <t>78708</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102197</t>
+          <t>103239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76545</t>
+          <t>77110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101519</t>
+          <t>101275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162216</t>
+          <t>162491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>197949</t>
+          <t>197276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>112138</t>
+          <t>111843</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>136056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112460</t>
+          <t>112383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138518</t>
+          <t>137514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>231649</t>
+          <t>229358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>267564</t>
+          <t>265411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>8212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19753</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37944</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16965</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>41019</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40462</t>
+          <t>40909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58497</t>
+          <t>59107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68991</t>
+          <t>70577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95516</t>
+          <t>93380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66178</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83909</t>
+          <t>83836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62453</t>
+          <t>61846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82101</t>
+          <t>81018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>134255</t>
+          <t>134799</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161275</t>
+          <t>160785</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15651</t>
+          <t>14820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>27711</t>
+          <t>27328</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70815</t>
+          <t>71446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36984</t>
+          <t>36918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56108</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93146</t>
+          <t>93384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>120888</t>
+          <t>120503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>96733</t>
+          <t>98282</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>119631</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>117627</t>
+          <t>117046</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>140323</t>
+          <t>139199</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>221657</t>
+          <t>222019</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>254359</t>
+          <t>253477</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,35%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>19959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25646</t>
+          <t>25354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42326</t>
+          <t>42645</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>629</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>597</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>42811</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65360</t>
+          <t>65846</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>43171</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>67985</t>
+          <t>67484</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91369</t>
+          <t>93284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>124853</t>
+          <t>126252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>206365</t>
+          <t>206134</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>244918</t>
+          <t>245191</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>206133</t>
+          <t>204672</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>246974</t>
+          <t>244689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>423299</t>
+          <t>424794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>481980</t>
+          <t>482486</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>323542</t>
+          <t>322592</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>364153</t>
+          <t>363332</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>350612</t>
+          <t>349122</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>391074</t>
+          <t>393685</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>683596</t>
+          <t>687107</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>744272</t>
+          <t>743408</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>33535</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53846</t>
+          <t>54832</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>37786</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59467</t>
+          <t>59853</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77175</t>
+          <t>76752</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>107317</t>
+          <t>107111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21528</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>25727</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45148</t>
+          <t>44639</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22086</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29283</t>
+          <t>29761</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17744</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31675</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36247</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56602</t>
+          <t>57523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71476</t>
+          <t>70664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89878</t>
+          <t>89772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67558</t>
+          <t>67685</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87090</t>
+          <t>87074</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145251</t>
+          <t>143362</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>173817</t>
+          <t>171634</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>59,84%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23888</t>
+          <t>24036</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>32365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>23630</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20973</t>
+          <t>21412</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>27990</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46398</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33669</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53416</t>
+          <t>55212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67490</t>
+          <t>66657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93528</t>
+          <t>94861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146137</t>
+          <t>145493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169422</t>
+          <t>168662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>160256</t>
+          <t>160387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186105</t>
+          <t>186658</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>314749</t>
+          <t>312257</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>348650</t>
+          <t>349041</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33097</t>
+          <t>34010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>17783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33474</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39267</t>
+          <t>38910</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62993</t>
+          <t>61470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,22%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>14746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21339</t>
+          <t>21461</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30517</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27371</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54271</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90028</t>
+          <t>90679</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108508</t>
+          <t>109255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>86587</t>
+          <t>86352</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106521</t>
+          <t>106513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>180313</t>
+          <t>181671</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209617</t>
+          <t>211165</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,82 +6092,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>26202</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>19343</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>35160</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>45587</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>35557</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>56038</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>14,47%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>17,79%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>26202</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>19093</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>34983</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>45587</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>35524</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>56278</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>13967</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10596</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>19795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>17672</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32508</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63211</t>
+          <t>64174</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89817</t>
+          <t>90740</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>111446</t>
+          <t>111714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>105853</t>
+          <t>106287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>126586</t>
+          <t>125744</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>204066</t>
+          <t>201583</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>233047</t>
+          <t>231954</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>22176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38601</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>21037</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>37235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46481</t>
+          <t>46697</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68975</t>
+          <t>69906</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,9%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36904</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57669</t>
+          <t>58211</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39899</t>
+          <t>40036</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62621</t>
+          <t>61568</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>82182</t>
+          <t>82245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113079</t>
+          <t>113342</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>93959</t>
+          <t>93072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>124048</t>
+          <t>123575</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97729</t>
+          <t>95540</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128231</t>
+          <t>127311</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>199452</t>
+          <t>198142</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>243748</t>
+          <t>243510</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>419102</t>
+          <t>416961</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>460534</t>
+          <t>458153</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,47 +7343,47 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>64,71%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>464208</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>442850</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>486970</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>62,04%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
           <t>59,19%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>65,04%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>464208</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>440432</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>484480</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>62,04%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>58,87%</t>
-        </is>
-      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>875414</t>
+          <t>870976</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>934704</t>
+          <t>933115</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>84730</t>
+          <t>84758</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>115960</t>
+          <t>114826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>80927</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>111423</t>
+          <t>111268</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>173734</t>
+          <t>174065</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>213997</t>
+          <t>216340</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35545</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32788</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>54443</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17069</t>
+          <t>17242</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23773</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32163</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>27893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44200</t>
+          <t>43484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28855</t>
+          <t>29502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45904</t>
+          <t>46513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>60315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83446</t>
+          <t>84111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,62%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>37797</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55154</t>
+          <t>54960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53915</t>
+          <t>54075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>79835</t>
+          <t>80315</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103453</t>
+          <t>104315</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>24502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14750</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29694</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>30692</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49264</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19505</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36028</t>
+          <t>37244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43464</t>
+          <t>44891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63817</t>
+          <t>64071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>48918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72027</t>
+          <t>70822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98060</t>
+          <t>98589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128642</t>
+          <t>127087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96935</t>
+          <t>96974</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118349</t>
+          <t>119700</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115399</t>
+          <t>115069</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140652</t>
+          <t>141722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>218992</t>
+          <t>220096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>254833</t>
+          <t>254522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,32%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47950</t>
+          <t>47975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>33264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53686</t>
+          <t>54531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68792</t>
+          <t>67494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96792</t>
+          <t>95246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15410</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>29770</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37263</t>
+          <t>36754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56489</t>
+          <t>56490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40695</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61293</t>
+          <t>59438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82076</t>
+          <t>82423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110510</t>
+          <t>110653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>82464</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>104621</t>
+          <t>104784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81756</t>
+          <t>81956</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105661</t>
+          <t>106167</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>170428</t>
+          <t>171362</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>202188</t>
+          <t>203016</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>39046</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>25471</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>43250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51965</t>
+          <t>51916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75695</t>
+          <t>76312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48075</t>
+          <t>47014</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37847</t>
+          <t>37675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55040</t>
+          <t>55113</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80367</t>
+          <t>79568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83213</t>
+          <t>84119</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>105520</t>
+          <t>106549</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>82593</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>105624</t>
+          <t>106604</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>173037</t>
+          <t>173608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>204831</t>
+          <t>205470</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,15%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>37694</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30859</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50673</t>
+          <t>49376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54959</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>81651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41239</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>62186</t>
+          <t>62021</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65391</t>
+          <t>64772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>88528</t>
+          <t>87736</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>118930</t>
+          <t>118757</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>154884</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>193112</t>
+          <t>193212</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155658</t>
+          <t>155689</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>193661</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>322963</t>
+          <t>321802</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>375382</t>
+          <t>375272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>319840</t>
+          <t>320830</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>363187</t>
+          <t>363861</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>339596</t>
+          <t>337743</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>384117</t>
+          <t>385978</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>672752</t>
+          <t>674256</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>733485</t>
+          <t>735607</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,96%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>99880</t>
+          <t>99945</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>131860</t>
+          <t>132736</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>120872</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>155140</t>
+          <t>153957</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>228038</t>
+          <t>228897</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>276008</t>
+          <t>276986</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>26841</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25422</t>
+          <t>26181</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45504</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
